--- a/weeklyRecord/每周工作明细.xlsx
+++ b/weeklyRecord/每周工作明细.xlsx
@@ -29,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
-  <si>
-    <t>工程每周工作内容记录表（2026.3.16-3.20）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
+  <si>
+    <t>工程每周工作内容记录表（2026.3.23-3.28）</t>
   </si>
   <si>
     <t>工程师：王昉立</t>
@@ -52,7 +52,7 @@
     <t>工作内容</t>
   </si>
   <si>
-    <t>蓝牙精油棒程序修改增加开关机逻辑</t>
+    <t>4按键长按遥控灯修改按按键逻辑</t>
   </si>
   <si>
     <t>待办事项</t>
@@ -61,28 +61,28 @@
     <t>星期二</t>
   </si>
   <si>
-    <t>FOC攀爬车电机调整刹车力度,限制Iq刹车时候的力度,增加刹车曲线</t>
+    <t>爬墙车生成测试模式改好</t>
   </si>
   <si>
     <t>星期三</t>
   </si>
   <si>
-    <t>写USB体感游戏棒程序，完成USB协议部分内容</t>
+    <t>攀爬车调整细节功能开机响几下问题</t>
   </si>
   <si>
     <t>星期四</t>
   </si>
   <si>
-    <t>写USB体感游戏棒程序,2.4G收发转换1配2通讯问题解决</t>
+    <t>无刷纠编机改程序</t>
   </si>
   <si>
     <t>星期五</t>
   </si>
   <si>
-    <t>调光灯的方案,初始开动,由以前风扇灯部分改遥控器和接收主控重新开始开发</t>
-  </si>
-  <si>
     <t>星期六</t>
+  </si>
+  <si>
+    <t>出差景荣解决对讲机距离近的问题</t>
   </si>
   <si>
     <t>星期日</t>
@@ -1353,7 +1353,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -1371,12 +1371,14 @@
     </row>
     <row r="14" ht="41" customHeight="1" spans="1:6">
       <c r="A14" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
       <c r="F14" s="13"/>
